--- a/Project Files/Reports/EPMA_TAPP_v86_Review_Workbook.xlsx
+++ b/Project Files/Reports/EPMA_TAPP_v86_Review_Workbook.xlsx
@@ -107,7 +107,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="17">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -184,11 +184,6 @@
         <fgColor rgb="00FBE5D6"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF2CC"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -230,7 +225,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -356,9 +351,6 @@
     <xf numFmtId="0" fontId="0" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -371,14 +363,8 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -454,26 +440,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <authors>
-    <author>TAPP review</author>
-  </authors>
-  <commentList>
-    <comment ref="F28" authorId="0" shapeId="0">
-      <text>
-        <t>Attested in 15 of 15 procedures as a single description. The procedure record cannot name samples or analysis points, so the per-unit detail appears only in the session column. Is this what a registering laboratory would expect to enter?</t>
-      </text>
-    </comment>
-    <comment ref="F103" authorId="0" shapeId="0">
-      <text>
-        <t>Not stated in any of the 15 procedures assessed. The procedure record cannot name samples or analysis points, so the per-unit detail appears only in the session column. Is this what a registering laboratory would expect to enter?</t>
-      </text>
-    </comment>
-  </commentList>
-</comments>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1030,7 +996,7 @@
     <row r="31" ht="45" customHeight="1">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Cells shaded pale yellow in the procedure column are the ones we are least sure of. The item repeats over samples or analysis points, which the procedure record cannot name, so the per-unit detail appears only in the session column. Hover over a shaded cell for what the literature shows, and tell us whether that is what a registering laboratory would expect to enter.</t>
+          <t>Where an item repeats over samples or analysis points, the procedure column leaves them out: the procedure record cannot name samples, so the per-unit detail appears only in the session column. Pre-Analysis Imaging and Screening, for example, is one description in the procedure and one per Sample Name in the session.</t>
         </is>
       </c>
     </row>
@@ -2918,7 +2884,7 @@
           <t>Imaging or screening performed before analysis to locate and select the units analysed, with the technique, instrument and settings, and how individual analyses are linked back to the images.</t>
         </is>
       </c>
-      <c r="F28" s="45" t="inlineStr">
+      <c r="F28" s="23" t="inlineStr">
         <is>
           <t>One value per procedure</t>
         </is>
@@ -3004,7 +2970,7 @@
         </is>
       </c>
       <c r="K29" s="41" t="n"/>
-      <c r="L29" s="46" t="inlineStr">
+      <c r="L29" s="45" t="inlineStr">
         <is>
           <t>Read-Only</t>
         </is>
@@ -3128,7 +3094,7 @@
         </is>
       </c>
       <c r="G31" s="39" t="n"/>
-      <c r="H31" s="47" t="inlineStr">
+      <c r="H31" s="46" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -3151,7 +3117,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="O31" s="48" t="inlineStr">
+      <c r="O31" s="47" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -3161,7 +3127,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="Q31" s="48" t="inlineStr">
+      <c r="Q31" s="47" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -3576,18 +3542,18 @@
         </is>
       </c>
       <c r="K39" s="41" t="n"/>
-      <c r="L39" s="46" t="inlineStr">
+      <c r="L39" s="45" t="inlineStr">
         <is>
           <t>Read-Only</t>
         </is>
       </c>
       <c r="M39" s="41" t="n"/>
-      <c r="N39" s="48" t="inlineStr">
+      <c r="N39" s="47" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="O39" s="48" t="inlineStr">
+      <c r="O39" s="47" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -3644,7 +3610,7 @@
         </is>
       </c>
       <c r="K40" s="41" t="n"/>
-      <c r="L40" s="46" t="inlineStr">
+      <c r="L40" s="45" t="inlineStr">
         <is>
           <t>Read-Only</t>
         </is>
@@ -3660,12 +3626,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="P40" s="48" t="inlineStr">
+      <c r="P40" s="47" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="Q40" s="48" t="inlineStr">
+      <c r="Q40" s="47" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -3944,7 +3910,7 @@
         </is>
       </c>
       <c r="K46" s="41" t="n"/>
-      <c r="L46" s="46" t="inlineStr">
+      <c r="L46" s="45" t="inlineStr">
         <is>
           <t>Read-Only</t>
         </is>
@@ -3955,7 +3921,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="O46" s="48" t="inlineStr">
+      <c r="O46" s="47" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -3965,7 +3931,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="Q46" s="48" t="inlineStr">
+      <c r="Q46" s="47" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -4023,7 +3989,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="O47" s="49" t="inlineStr">
+      <c r="O47" s="48" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -4033,7 +3999,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="Q47" s="49" t="inlineStr">
+      <c r="Q47" s="48" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -4091,7 +4057,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="O48" s="49" t="inlineStr">
+      <c r="O48" s="48" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -4101,7 +4067,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="Q48" s="49" t="inlineStr">
+      <c r="Q48" s="48" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -4159,7 +4125,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="O49" s="49" t="inlineStr">
+      <c r="O49" s="48" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -4169,7 +4135,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="Q49" s="49" t="inlineStr">
+      <c r="Q49" s="48" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -4227,7 +4193,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="O50" s="49" t="inlineStr">
+      <c r="O50" s="48" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -4237,7 +4203,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="Q50" s="49" t="inlineStr">
+      <c r="Q50" s="48" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -4284,13 +4250,13 @@
         </is>
       </c>
       <c r="K51" s="41" t="n"/>
-      <c r="L51" s="46" t="inlineStr">
+      <c r="L51" s="45" t="inlineStr">
         <is>
           <t>Read-Only</t>
         </is>
       </c>
       <c r="M51" s="41" t="n"/>
-      <c r="N51" s="48" t="inlineStr">
+      <c r="N51" s="47" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -4300,7 +4266,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="P51" s="48" t="inlineStr">
+      <c r="P51" s="47" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -4358,7 +4324,7 @@
         </is>
       </c>
       <c r="M52" s="29" t="n"/>
-      <c r="N52" s="49" t="inlineStr">
+      <c r="N52" s="48" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -4368,7 +4334,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="P52" s="49" t="inlineStr">
+      <c r="P52" s="48" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -4426,7 +4392,7 @@
         </is>
       </c>
       <c r="M53" s="29" t="n"/>
-      <c r="N53" s="49" t="inlineStr">
+      <c r="N53" s="48" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -4436,7 +4402,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="P53" s="49" t="inlineStr">
+      <c r="P53" s="48" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -4624,7 +4590,7 @@
         </is>
       </c>
       <c r="K56" s="41" t="n"/>
-      <c r="L56" s="46" t="inlineStr">
+      <c r="L56" s="45" t="inlineStr">
         <is>
           <t>Read-Only</t>
         </is>
@@ -4692,7 +4658,7 @@
         </is>
       </c>
       <c r="K57" s="41" t="n"/>
-      <c r="L57" s="46" t="inlineStr">
+      <c r="L57" s="45" t="inlineStr">
         <is>
           <t>Read-Only</t>
         </is>
@@ -4828,18 +4794,18 @@
         </is>
       </c>
       <c r="K59" s="41" t="n"/>
-      <c r="L59" s="46" t="inlineStr">
+      <c r="L59" s="45" t="inlineStr">
         <is>
           <t>Read-Only</t>
         </is>
       </c>
       <c r="M59" s="41" t="n"/>
-      <c r="N59" s="48" t="inlineStr">
+      <c r="N59" s="47" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="O59" s="48" t="inlineStr">
+      <c r="O59" s="47" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -4902,12 +4868,12 @@
         </is>
       </c>
       <c r="M60" s="29" t="n"/>
-      <c r="N60" s="49" t="inlineStr">
+      <c r="N60" s="48" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="O60" s="49" t="inlineStr">
+      <c r="O60" s="48" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -4970,12 +4936,12 @@
         </is>
       </c>
       <c r="M61" s="29" t="n"/>
-      <c r="N61" s="49" t="inlineStr">
+      <c r="N61" s="48" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="O61" s="49" t="inlineStr">
+      <c r="O61" s="48" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -5038,12 +5004,12 @@
         </is>
       </c>
       <c r="M62" s="29" t="n"/>
-      <c r="N62" s="49" t="inlineStr">
+      <c r="N62" s="48" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="O62" s="49" t="inlineStr">
+      <c r="O62" s="48" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -5100,18 +5066,18 @@
         </is>
       </c>
       <c r="K63" s="41" t="n"/>
-      <c r="L63" s="46" t="inlineStr">
+      <c r="L63" s="45" t="inlineStr">
         <is>
           <t>Read-Only</t>
         </is>
       </c>
       <c r="M63" s="41" t="n"/>
-      <c r="N63" s="48" t="inlineStr">
+      <c r="N63" s="47" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="O63" s="48" t="inlineStr">
+      <c r="O63" s="47" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -5121,7 +5087,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="Q63" s="48" t="inlineStr">
+      <c r="Q63" s="47" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -5174,12 +5140,12 @@
         </is>
       </c>
       <c r="M64" s="29" t="n"/>
-      <c r="N64" s="49" t="inlineStr">
+      <c r="N64" s="48" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="O64" s="49" t="inlineStr">
+      <c r="O64" s="48" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -5189,7 +5155,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="Q64" s="49" t="inlineStr">
+      <c r="Q64" s="48" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -5242,12 +5208,12 @@
         </is>
       </c>
       <c r="M65" s="29" t="n"/>
-      <c r="N65" s="49" t="inlineStr">
+      <c r="N65" s="48" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="O65" s="49" t="inlineStr">
+      <c r="O65" s="48" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -5257,7 +5223,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="Q65" s="49" t="inlineStr">
+      <c r="Q65" s="48" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -5310,12 +5276,12 @@
         </is>
       </c>
       <c r="M66" s="29" t="n"/>
-      <c r="N66" s="49" t="inlineStr">
+      <c r="N66" s="48" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="O66" s="49" t="inlineStr">
+      <c r="O66" s="48" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -5325,7 +5291,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="Q66" s="49" t="inlineStr">
+      <c r="Q66" s="48" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -5383,17 +5349,17 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="O67" s="48" t="inlineStr">
+      <c r="O67" s="47" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="P67" s="48" t="inlineStr">
+      <c r="P67" s="47" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="Q67" s="48" t="inlineStr">
+      <c r="Q67" s="47" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -5440,7 +5406,7 @@
         </is>
       </c>
       <c r="K68" s="41" t="n"/>
-      <c r="L68" s="46" t="inlineStr">
+      <c r="L68" s="45" t="inlineStr">
         <is>
           <t>Read-Only</t>
         </is>
@@ -5456,12 +5422,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="P68" s="48" t="inlineStr">
+      <c r="P68" s="47" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="Q68" s="48" t="inlineStr">
+      <c r="Q68" s="47" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -5514,7 +5480,7 @@
         </is>
       </c>
       <c r="M69" s="41" t="n"/>
-      <c r="N69" s="48" t="inlineStr">
+      <c r="N69" s="47" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -5524,7 +5490,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="P69" s="48" t="inlineStr">
+      <c r="P69" s="47" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -5582,7 +5548,7 @@
         </is>
       </c>
       <c r="M70" s="41" t="n"/>
-      <c r="N70" s="48" t="inlineStr">
+      <c r="N70" s="47" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -5592,7 +5558,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="P70" s="48" t="inlineStr">
+      <c r="P70" s="47" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -5650,7 +5616,7 @@
         </is>
       </c>
       <c r="M71" s="29" t="n"/>
-      <c r="N71" s="49" t="inlineStr">
+      <c r="N71" s="48" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -5660,7 +5626,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="P71" s="49" t="inlineStr">
+      <c r="P71" s="48" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -5718,7 +5684,7 @@
         </is>
       </c>
       <c r="M72" s="29" t="n"/>
-      <c r="N72" s="49" t="inlineStr">
+      <c r="N72" s="48" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -5728,7 +5694,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="P72" s="49" t="inlineStr">
+      <c r="P72" s="48" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -5786,7 +5752,7 @@
         </is>
       </c>
       <c r="M73" s="29" t="n"/>
-      <c r="N73" s="49" t="inlineStr">
+      <c r="N73" s="48" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -5796,7 +5762,7 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="P73" s="49" t="inlineStr">
+      <c r="P73" s="48" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -6488,18 +6454,18 @@
         </is>
       </c>
       <c r="K85" s="41" t="n"/>
-      <c r="L85" s="46" t="inlineStr">
+      <c r="L85" s="45" t="inlineStr">
         <is>
           <t>Read-Only</t>
         </is>
       </c>
       <c r="M85" s="41" t="n"/>
-      <c r="N85" s="48" t="inlineStr">
+      <c r="N85" s="47" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="O85" s="48" t="inlineStr">
+      <c r="O85" s="47" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -6556,7 +6522,7 @@
         </is>
       </c>
       <c r="K86" s="41" t="n"/>
-      <c r="L86" s="46" t="inlineStr">
+      <c r="L86" s="45" t="inlineStr">
         <is>
           <t>Read-Only</t>
         </is>
@@ -6572,12 +6538,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="P86" s="48" t="inlineStr">
+      <c r="P86" s="47" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="Q86" s="48" t="inlineStr">
+      <c r="Q86" s="47" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -6884,7 +6850,7 @@
         </is>
       </c>
       <c r="G91" s="39" t="n"/>
-      <c r="H91" s="47" t="inlineStr">
+      <c r="H91" s="46" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7128,7 +7094,7 @@
         </is>
       </c>
       <c r="K96" s="41" t="n"/>
-      <c r="L96" s="46" t="inlineStr">
+      <c r="L96" s="45" t="inlineStr">
         <is>
           <t>Read-Only</t>
         </is>
@@ -7586,7 +7552,7 @@
           <t>The uncertainty predicted from counting statistics, including the counts on any background or blank subtracted, with the sigma level stated.</t>
         </is>
       </c>
-      <c r="F103" s="50" t="inlineStr">
+      <c r="F103" s="35" t="inlineStr">
         <is>
           <t>One value per Reported Variable</t>
         </is>
@@ -7660,7 +7626,7 @@
         </is>
       </c>
       <c r="G104" s="39" t="n"/>
-      <c r="H104" s="47" t="inlineStr">
+      <c r="H104" s="46" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7688,12 +7654,12 @@
           <t>✓</t>
         </is>
       </c>
-      <c r="P104" s="48" t="inlineStr">
+      <c r="P104" s="47" t="inlineStr">
         <is>
           <t>–</t>
         </is>
       </c>
-      <c r="Q104" s="48" t="inlineStr">
+      <c r="Q104" s="47" t="inlineStr">
         <is>
           <t>–</t>
         </is>
@@ -7728,7 +7694,7 @@
         </is>
       </c>
       <c r="G105" s="39" t="n"/>
-      <c r="H105" s="47" t="inlineStr">
+      <c r="H105" s="46" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
@@ -7925,7 +7891,6 @@
   </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="8" fitToHeight="0" fitToWidth="1"/>
-  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
@@ -7946,27 +7911,27 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="51" t="inlineStr">
+      <c r="A1" s="49" t="inlineStr">
         <is>
           <t>#</t>
         </is>
       </c>
-      <c r="B1" s="51" t="inlineStr">
+      <c r="B1" s="49" t="inlineStr">
         <is>
           <t>Metadata item</t>
         </is>
       </c>
-      <c r="C1" s="51" t="inlineStr">
+      <c r="C1" s="49" t="inlineStr">
         <is>
           <t>TAPP "Keyed By" (Column I)</t>
         </is>
       </c>
-      <c r="D1" s="51" t="inlineStr">
+      <c r="D1" s="49" t="inlineStr">
         <is>
           <t>Structure — procedure record</t>
         </is>
       </c>
-      <c r="E1" s="51" t="inlineStr">
+      <c r="E1" s="49" t="inlineStr">
         <is>
           <t>Structure — session record</t>
         </is>
@@ -8501,7 +8466,7 @@
           <t>sample</t>
         </is>
       </c>
-      <c r="D21" s="52" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>One value per procedure</t>
         </is>
@@ -8582,7 +8547,7 @@
           <t>defines: sample &gt; sampling unit</t>
         </is>
       </c>
-      <c r="D24" s="52" t="inlineStr">
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -8609,7 +8574,7 @@
           <t>sample &gt; sampling unit</t>
         </is>
       </c>
-      <c r="D25" s="52" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -8636,7 +8601,7 @@
           <t>sample</t>
         </is>
       </c>
-      <c r="D26" s="52" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -8690,7 +8655,7 @@
           <t>sample</t>
         </is>
       </c>
-      <c r="D28" s="52" t="inlineStr">
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>One value per procedure</t>
         </is>
@@ -9095,7 +9060,7 @@
           <t>sample &gt; sampling unit</t>
         </is>
       </c>
-      <c r="D43" s="52" t="inlineStr">
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>One value per procedure</t>
         </is>
@@ -9122,7 +9087,7 @@
           <t>sample &gt; sampling unit</t>
         </is>
       </c>
-      <c r="D44" s="52" t="inlineStr">
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>One value per procedure</t>
         </is>
@@ -9149,7 +9114,7 @@
           <t>sample &gt; sampling unit</t>
         </is>
       </c>
-      <c r="D45" s="52" t="inlineStr">
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>One value per procedure</t>
         </is>
@@ -10067,7 +10032,7 @@
           <t>combined result</t>
         </is>
       </c>
-      <c r="D79" s="52" t="inlineStr">
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>One value per procedure</t>
         </is>
@@ -10418,7 +10383,7 @@
           <t>sample &gt; sampling unit x reported property</t>
         </is>
       </c>
-      <c r="D92" s="52" t="inlineStr">
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>One value per Reported Variable</t>
         </is>
@@ -10472,7 +10437,7 @@
           <t>combined result x reported property</t>
         </is>
       </c>
-      <c r="D94" s="52" t="inlineStr">
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
@@ -10499,7 +10464,7 @@
           <t>combined result x reported property</t>
         </is>
       </c>
-      <c r="D95" s="52" t="inlineStr">
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
